--- a/test-data/TestCasesDoc.xlsx
+++ b/test-data/TestCasesDoc.xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000"/>
+    <workbookView windowWidth="22188" windowHeight="9000" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1485,4 +1487,26 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/test-data/TestCasesDoc.xlsx
+++ b/test-data/TestCasesDoc.xlsx
@@ -4,12 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1487,26 +1485,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>